--- a/JIG-template.xlsx
+++ b/JIG-template.xlsx
@@ -5,7 +5,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Issue主檔" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="組別頁面" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Task一覽" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mission一覽" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3946,7 +3946,7 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" style="6" min="1" max="1"/>
+    <col width="14" customWidth="1" style="6" min="1" max="1"/>
     <col width="38" customWidth="1" style="6" min="2" max="2"/>
     <col width="12" customWidth="1" style="6" min="3" max="3"/>
     <col width="12" customWidth="1" style="6" min="4" max="4"/>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B1" s="7" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="C1" s="7" t="inlineStr">
@@ -4001,7 +4001,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>戰略-1-T1</t>
+          <t>戰略-1-M1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4028,7 +4028,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>戰略-1-T2</t>
+          <t>戰略-1-M2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4055,7 +4055,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>戰略-2-T1</t>
+          <t>戰略-2-M1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4082,7 +4082,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CX-1-T1</t>
+          <t>CX-1-M1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
